--- a/data/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ18"/>
+  <dimension ref="A1:AJ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2702,8 +2702,114 @@
       <c r="AI18" s="2" t="inlineStr"/>
       <c r="AJ18" s="2" t="inlineStr"/>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>c37f424aa4bb4d87</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>f0fcbc1453d1a656a25d9f456c501ac849c71b8ef6259b2f4e05c512bd7040ac</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0.687940</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0.559471</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0.128469</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T15:51:46.912541Z</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>migrated_from=data/research/dota2.xlsx;original_pick_id=c37f424aa4bb4d87;original_record_type=QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="2" t="inlineStr"/>
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="2" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ18"/>
+  <autoFilter ref="A1:AJ19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ19"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2808,8 +2808,110 @@
       <c r="AI19" s="2" t="inlineStr"/>
       <c r="AJ19" s="2" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>7722305e9c6d4c43</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>8e17bc625b6f663721d0cd0b27f30cf8017a2cbaa61c81881824fbb2600f16d7</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>0.687866</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr"/>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>0.12839463436123344</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:09:15.062801Z</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="2" t="inlineStr"/>
+      <c r="AG20" s="2" t="inlineStr"/>
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="2" t="inlineStr"/>
+      <c r="AJ20" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ19"/>
+  <autoFilter ref="A1:AJ20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -2910,8 +2910,110 @@
       <c r="AI20" s="2" t="inlineStr"/>
       <c r="AJ20" s="2" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>a3b344188cc545f0</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>cb2508545871cd245c79cd37a7ddf28f5f869bf875eba85e1d6069b628af9a62</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0.687866</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>0.12839463436123344</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:25:03.516712Z</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="2" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ20"/>
+  <autoFilter ref="A1:AJ21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ21"/>
+  <dimension ref="A1:AJ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3012,8 +3012,3414 @@
       <c r="AI21" s="2" t="inlineStr"/>
       <c r="AJ21" s="2" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>b0c046a4f9f34bb3</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>9c5f1e0498568c8c9d9ce690d9b28bbb93b8c82b61f0585c72a5fa45be3b22f5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0.687866</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0.12839463436123344</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:55:15.811302Z</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="2" t="inlineStr"/>
+      <c r="AH22" s="2" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>4150b045c7fe48b8</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>c5e574fce81b754746d25bd1be4a70938cce553267554fb8aa28996355ec028c</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0.688438</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>0.12896663436123346</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T19:32:07.176804Z</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="2" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="2" t="inlineStr"/>
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="2" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>44cf77197c7140c6</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>0.688438</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>0.10860606722689081</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:10.490431Z</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="2" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>18064e31bd214966</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0.622594</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0.42016806722689076</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>0.20242593277310922</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:11.536317Z</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="2" t="inlineStr"/>
+      <c r="AG25" s="2" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>1b12c967bae74678</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>70046</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0.838894</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>0.15838281789137387</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:12.000249Z</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="2" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="2" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>30b099df64584e07</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>-0.04180400000000006</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:12.498644Z</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="2" t="inlineStr"/>
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="2" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>6c0c5d7ead794bd1</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>0.04029456807511733</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:13.488700Z</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="2" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="2" t="inlineStr"/>
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="2" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>6ef5bad5217c4e56</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3aec5c18e4baa0f9a1c7ddffe59287913cd115137d2a3b4af2f4e69f0595f97f</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>70306</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>0.572663</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>0.6805111821086262</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>-0.10784818210862612</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-02T23:17:13.972415Z</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="2" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="2" t="inlineStr"/>
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="2" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>b493643bfa364a82</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>6d4544b49d1d638f1deb4234c0e0c01fa8fbae11f01c2a2fc60b31712569fb95</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0.688438</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>0.079063</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:24.674109Z</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="2" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="2" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>003bf58b85ad481e</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>6d4544b49d1d638f1deb4234c0e0c01fa8fbae11f01c2a2fc60b31712569fb95</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>0.622594</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>0.23196899999999998</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:25.733915Z</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="2" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="2" t="inlineStr"/>
+      <c r="AH31" s="2" t="inlineStr"/>
+      <c r="AI31" s="2" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>5babc92f78294832</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>6d4544b49d1d638f1deb4234c0e0c01fa8fbae11f01c2a2fc60b31712569fb95</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>-0.051178999999999975</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:26.845751Z</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr"/>
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>a6bf76ac1ef24187</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>6d4544b49d1d638f1deb4234c0e0c01fa8fbae11f01c2a2fc60b31712569fb95</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>0.78276</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>0.08306030030030032</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:27.432081Z</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>3ddf207cd2024e8b</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>6d4544b49d1d638f1deb4234c0e0c01fa8fbae11f01c2a2fc60b31712569fb95</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>0.02126145045045047</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T02:47:27.967852Z</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>07b14d8d6b97410f</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>69530</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>0.688438</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>0.058808370370370455</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:21.088131Z</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>0.630000</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>0.000370</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>1.1765</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:06:24.173741Z</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>9349713cf7124987</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0.622594</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>0.23196899999999998</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:22.245034Z</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="2" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>69b8b33a4db949b3</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>-0.07143362962962951</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:23.543914Z</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>e3ef1956ab604d09</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0.78276</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>0.08306030030030032</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:24.118010Z</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>0b55ebf9de74458a</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>bf20998d8a70c3832fd09ea459020acc93ce47c0fe8f683c0d8face894c2cb28</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>0.031640493087557564</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T04:20:24.656879Z</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>a6b28eb59dc04488</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>70303</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>0.622594</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.390625</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>0.23196899999999998</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:30.412423Z</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>0.390000</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>-0.000625</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>-1.5000</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:55:42.679211Z</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>b5d9f7a488cd4ea9</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>-0.07143362962962951</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:31.491970Z</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>a383ea6f5ba24e6a</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>0.78276</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>0.08306030030030032</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:32.038017Z</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>07525e97ea1c49e9</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>533fea08f6899886856a22c8b82fe2bc1d4c49576971024283434d4b7315bbc9</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.5391705069124424</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>0.031640493087557564</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:32:32.495232Z</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>3b8fa684b2ab4f08</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>df737ccc747168411051ce1a17c4ba0d065ba4d5b92bad2d63306ee6a3d852ad</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>-0.03196793442622947</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:15:50.661222Z</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>05da362bd66b40b0</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>df737ccc747168411051ce1a17c4ba0d065ba4d5b92bad2d63306ee6a3d852ad</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>0.78276</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>0.08306030030030032</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:15:51.151586Z</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>daec87ec9c2145a3</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>df737ccc747168411051ce1a17c4ba0d065ba4d5b92bad2d63306ee6a3d852ad</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>0.04029456807511733</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:15:51.693288Z</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>90eee8ce1e104d9f</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>7622acb01e75f8c072abce75d7db6c9e6cede883a38c71cb50ddb09cb5b70653</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>0.558196</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>-0.03196793442622947</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:14.997846Z</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>8304fc9456aa4998</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>7622acb01e75f8c072abce75d7db6c9e6cede883a38c71cb50ddb09cb5b70653</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>0.78276</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>0.08306030030030032</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:15.479941Z</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>b0fe6ce896024c50</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>7622acb01e75f8c072abce75d7db6c9e6cede883a38c71cb50ddb09cb5b70653</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>0.570811</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>0.04029456807511733</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:49:16.010693Z</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>345b9d01989c4ac9</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>528639205c5899c0cdf1bae7bf1adfb5d019bc11e79b9bc778f8eb3bb742ae6e</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>70304</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>0.557781</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>-0.032382934426229526</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:42.011106Z</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>d23ccfcff21e4996</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>528639205c5899c0cdf1bae7bf1adfb5d019bc11e79b9bc778f8eb3bb742ae6e</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>0.75532</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>0.055620300300300296</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:42.630829Z</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>d70ff69b016b4939</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>528639205c5899c0cdf1bae7bf1adfb5d019bc11e79b9bc778f8eb3bb742ae6e</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>0.571416</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>0.04089956807511741</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T10:59:43.200159Z</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="2" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>16b42251580745c2</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>70380</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>0.75532</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>0.055620300300300296</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:33.121525Z</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="2" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>59b0231168784055</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>9f83c860ce6adddad784676b2958b8c4421adf6e3abacd5545efbed1bb0cde1d</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>70305</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0.571416</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>0.04089956807511741</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T13:30:33.684542Z</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-03T15:00:00Z</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr"/>
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="2" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ21"/>
+  <autoFilter ref="A1:AJ54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/model_ledgers/dota2-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ54"/>
+  <dimension ref="A1:AJ55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6418,8 +6418,110 @@
       <c r="AI54" s="2" t="inlineStr"/>
       <c r="AJ54" s="2" t="inlineStr"/>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>65ce496f3b984c52</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>ceea9688d905d0ad390cdd3daf87ff0098fa5c01330be03572f98270d67ece12</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>77167</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>0.738453</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>0.03875330030030033</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T19:34:35.104443Z</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="2" t="inlineStr"/>
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="2" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ54"/>
+  <autoFilter ref="A1:AJ55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/model_ledgers/dota2-tiered-elo.xlsx
+++ b/data/model_ledgers/dota2-tiered-elo.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ55"/>
+  <dimension ref="A1:AJ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6520,8 +6520,1244 @@
       <c r="AI55" s="2" t="inlineStr"/>
       <c r="AJ55" s="2" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>9d10198e77a649aa</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>3a1a2b913a7c526741b38a48f0957f5889bc186a2bd05c8fa45d935778de3be1</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>77167</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0.738336</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>0.6996996996996997</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>0.0386363003003003</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:33:41.354194Z</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>0.8584</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T10:05:42.261704Z</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr"/>
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="2" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>ef58b5db7dd04e0f</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>9421e231807d8939d2db85da8b00dd77f261c24d811f5e8d085c5b1c834bb8b1</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>80486</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0.671606</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0.5798319327731092</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>0.09177406722689085</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:47:13.538076Z</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="2" t="inlineStr"/>
+      <c r="AH57" s="2" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>3da1e25196b34ced</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>9421e231807d8939d2db85da8b00dd77f261c24d811f5e8d085c5b1c834bb8b1</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>80487</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>0.799642</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>0.5098039215686274</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>0.28983807843137255</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:47:14.011820Z</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="2" t="inlineStr"/>
+      <c r="AH58" s="2" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>c3a0d55edb194545</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>9421e231807d8939d2db85da8b00dd77f261c24d811f5e8d085c5b1c834bb8b1</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>80488</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>0.523317</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>-0.036154365638766506</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T13:47:14.552591Z</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="2" t="inlineStr"/>
+      <c r="AH59" s="2" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
+      <c r="AJ59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>6e63429bdac84492</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>5519a253fa80c1d9e1cb38565b6a7c22337640a8aa34de9a86e0db9e96c94f5b</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>80486</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0.671619</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>0.051847136882129274</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:53:32.213458Z</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr"/>
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr"/>
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="2" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
+      <c r="AJ60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>0f690c250ae143e5</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>5519a253fa80c1d9e1cb38565b6a7c22337640a8aa34de9a86e0db9e96c94f5b</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>80487</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>0.799401</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>0.20923706557377053</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:53:32.708468Z</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr"/>
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="2" t="inlineStr"/>
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="2" t="inlineStr"/>
+      <c r="AH61" s="2" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
+      <c r="AJ61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>a244138ac6dd44a8</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>5519a253fa80c1d9e1cb38565b6a7c22337640a8aa34de9a86e0db9e96c94f5b</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>80488</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>0.523705</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>-0.03576636563876656</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:53:33.231491Z</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="2" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
+      <c r="AJ62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>70d01ead3dc24b0a</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>80486</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>0.671599</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>0.051827136882129254</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:16:21.311272Z</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr"/>
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="2" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>015dd42fd39248fb</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>80487</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>0.79937</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>0.20920606557377053</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:16:21.914112Z</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AG64" s="2" t="inlineStr"/>
+      <c r="AH64" s="2" t="inlineStr"/>
+      <c r="AI64" s="2" t="inlineStr"/>
+      <c r="AJ64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>a1dd00030c5b4987</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>80488</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>0.523704</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>0.5594713656387665</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>-0.03576736563876659</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:16:22.422111Z</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T02:00:00Z</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="2" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AG65" s="2" t="inlineStr"/>
+      <c r="AH65" s="2" t="inlineStr"/>
+      <c r="AI65" s="2" t="inlineStr"/>
+      <c r="AJ65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>089f94507c2a4f7b</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>80587</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>0.630076</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>0.5305164319248826</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>0.09955956807511734</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:16:22.989356Z</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="2" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
+      <c r="AG66" s="2" t="inlineStr"/>
+      <c r="AH66" s="2" t="inlineStr"/>
+      <c r="AI66" s="2" t="inlineStr"/>
+      <c r="AJ66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>8bf3c38acc2345a7</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>34400c15f5679c060458bb6b5dbe8cc623f1b008cf64e0b428c51611a5c66f4e</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>dota2-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>80588</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>0.578638</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>0.5495495495495495</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>0.029088450450450498</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:16:23.502827Z</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-14T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="2" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+      <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AG67" s="2" t="inlineStr"/>
+      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AI67" s="2" t="inlineStr"/>
+      <c r="AJ67" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ55"/>
+  <autoFilter ref="A1:AJ67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>